--- a/exports/performance_run_10000.xlsx
+++ b/exports/performance_run_10000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.187</v>
+        <v>0.208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.199</v>
+        <v>0.225</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>11640</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="3">
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.321</v>
+        <v>0.337</v>
       </c>
       <c r="E3" t="n">
-        <v>0.386</v>
+        <v>0.373</v>
       </c>
       <c r="F3" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>11580</v>
+        <v>11610</v>
       </c>
     </row>
     <row r="4">
@@ -545,19 +545,19 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.065</v>
+        <v>0.054</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5">
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>4.54</v>
+        <v>4.463</v>
       </c>
       <c r="E5" t="n">
-        <v>4.693</v>
+        <v>4.526</v>
       </c>
       <c r="F5" t="n">
-        <v>4.56</v>
+        <v>4.458</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.452</v>
+        <v>0.409</v>
       </c>
       <c r="E6" t="n">
-        <v>0.584</v>
+        <v>0.445</v>
       </c>
       <c r="F6" t="n">
-        <v>0.473</v>
+        <v>0.422</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>20610</v>
+        <v>20460</v>
       </c>
     </row>
     <row r="7">
@@ -635,13 +635,13 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>2.142</v>
+        <v>2.001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.188</v>
+        <v>2.138</v>
       </c>
       <c r="F7" t="n">
-        <v>2.149</v>
+        <v>2.032</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>7.255</v>
+        <v>6.454</v>
       </c>
       <c r="E8" t="n">
-        <v>7.727</v>
+        <v>7.728</v>
       </c>
       <c r="F8" t="n">
-        <v>6.97</v>
+        <v>6.667</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.302</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.321</v>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>11610</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="10">
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>0.162</v>
+        <v>0.149</v>
       </c>
       <c r="E10" t="n">
-        <v>0.188</v>
+        <v>0.178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.165</v>
+        <v>0.153</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>11610</v>
+        <v>11640</v>
       </c>
     </row>
     <row r="11">
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>4.567</v>
+        <v>3.128</v>
       </c>
       <c r="E11" t="n">
-        <v>6.101</v>
+        <v>3.333</v>
       </c>
       <c r="F11" t="n">
-        <v>4.746</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>50130</v>
+        <v>50640</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>5.247</v>
+        <v>3.656</v>
       </c>
       <c r="E12" t="n">
-        <v>6.052</v>
+        <v>3.979</v>
       </c>
       <c r="F12" t="n">
-        <v>5.294</v>
+        <v>3.517</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>3.634</v>
+        <v>3.395</v>
       </c>
       <c r="E13" t="n">
-        <v>3.811</v>
+        <v>4.237</v>
       </c>
       <c r="F13" t="n">
-        <v>3.635</v>
+        <v>3.433</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>2.762</v>
+        <v>2.573</v>
       </c>
       <c r="E14" t="n">
-        <v>2.983</v>
+        <v>2.885</v>
       </c>
       <c r="F14" t="n">
-        <v>2.772</v>
+        <v>2.514</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>8.114000000000001</v>
+        <v>7.692</v>
       </c>
       <c r="E15" t="n">
-        <v>9.945</v>
+        <v>8.667</v>
       </c>
       <c r="F15" t="n">
-        <v>8.553000000000001</v>
+        <v>7.852</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>8.725</v>
+        <v>6.256</v>
       </c>
       <c r="E16" t="n">
-        <v>9.568</v>
+        <v>7.107</v>
       </c>
       <c r="F16" t="n">
-        <v>8.509</v>
+        <v>6.15</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>4.733</v>
+        <v>4.153</v>
       </c>
       <c r="E17" t="n">
-        <v>5.617</v>
+        <v>4.741</v>
       </c>
       <c r="F17" t="n">
-        <v>4.697</v>
+        <v>4.231</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>7.772</v>
+        <v>6.307</v>
       </c>
       <c r="E18" t="n">
-        <v>9.223000000000001</v>
+        <v>8.903</v>
       </c>
       <c r="F18" t="n">
-        <v>7.865</v>
+        <v>7.134</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>3.441</v>
+        <v>2.808</v>
       </c>
       <c r="E19" t="n">
-        <v>3.512</v>
+        <v>3.16</v>
       </c>
       <c r="F19" t="n">
-        <v>3.422</v>
+        <v>2.859</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>3.558</v>
+        <v>4.582</v>
       </c>
       <c r="E20" t="n">
-        <v>4.582</v>
+        <v>6.979</v>
       </c>
       <c r="F20" t="n">
-        <v>3.705</v>
+        <v>4.834</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>7.405</v>
+        <v>6.037</v>
       </c>
       <c r="E21" t="n">
-        <v>8.271000000000001</v>
+        <v>7.621</v>
       </c>
       <c r="F21" t="n">
-        <v>7.535</v>
+        <v>6.168</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>0.205</v>
+        <v>0.155</v>
       </c>
       <c r="E22" t="n">
-        <v>0.242</v>
+        <v>0.161</v>
       </c>
       <c r="F22" t="n">
-        <v>0.213</v>
+        <v>0.159</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>11610</v>
+        <v>11640</v>
       </c>
     </row>
     <row r="23">
@@ -1115,13 +1115,13 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>0.297</v>
+        <v>0.313</v>
       </c>
       <c r="E23" t="n">
-        <v>0.34</v>
+        <v>0.355</v>
       </c>
       <c r="F23" t="n">
-        <v>0.301</v>
+        <v>0.313</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1145,19 +1145,19 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="E24" t="n">
-        <v>0.045</v>
+        <v>0.041</v>
       </c>
       <c r="F24" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25">
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>5.789</v>
+        <v>5.749</v>
       </c>
       <c r="E25" t="n">
-        <v>6.016</v>
+        <v>5.946</v>
       </c>
       <c r="F25" t="n">
-        <v>5.813</v>
+        <v>5.776</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>0.427</v>
+        <v>0.362</v>
       </c>
       <c r="E26" t="n">
-        <v>0.546</v>
+        <v>0.409</v>
       </c>
       <c r="F26" t="n">
-        <v>0.436</v>
+        <v>0.355</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>12960</v>
+        <v>12450</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>3.322</v>
+        <v>3.21</v>
       </c>
       <c r="E27" t="n">
-        <v>3.645</v>
+        <v>3.327</v>
       </c>
       <c r="F27" t="n">
-        <v>3.334</v>
+        <v>3.229</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>15990</v>
+        <v>15870</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>2.922</v>
+        <v>4.046</v>
       </c>
       <c r="E28" t="n">
-        <v>3.031</v>
+        <v>4.416</v>
       </c>
       <c r="F28" t="n">
-        <v>2.935</v>
+        <v>3.992</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="29">
@@ -1295,13 +1295,13 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>0.274</v>
+        <v>0.254</v>
       </c>
       <c r="E29" t="n">
-        <v>0.316</v>
+        <v>0.416</v>
       </c>
       <c r="F29" t="n">
-        <v>0.27</v>
+        <v>0.285</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>0.346</v>
+        <v>0.327</v>
       </c>
       <c r="E30" t="n">
-        <v>0.388</v>
+        <v>0.383</v>
       </c>
       <c r="F30" t="n">
-        <v>0.353</v>
+        <v>0.342</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>11610</v>
+        <v>11580</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>1.141</v>
+        <v>2.476</v>
       </c>
       <c r="E31" t="n">
-        <v>1.379</v>
+        <v>2.797</v>
       </c>
       <c r="F31" t="n">
-        <v>1.183</v>
+        <v>2.529</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>15720</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>1.119</v>
+        <v>1.062</v>
       </c>
       <c r="E32" t="n">
-        <v>1.324</v>
+        <v>1.248</v>
       </c>
       <c r="F32" t="n">
-        <v>1.179</v>
+        <v>1.101</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>2.067</v>
+        <v>2.106</v>
       </c>
       <c r="E33" t="n">
-        <v>2.212</v>
+        <v>2.283</v>
       </c>
       <c r="F33" t="n">
-        <v>2.099</v>
+        <v>2.131</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>1.084</v>
+        <v>1.042</v>
       </c>
       <c r="E34" t="n">
-        <v>1.257</v>
+        <v>1.091</v>
       </c>
       <c r="F34" t="n">
-        <v>1.109</v>
+        <v>1.05</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>5.884</v>
+        <v>5.947</v>
       </c>
       <c r="E35" t="n">
-        <v>6.267</v>
+        <v>6.278</v>
       </c>
       <c r="F35" t="n">
-        <v>5.911</v>
+        <v>5.982</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>1.451</v>
+        <v>1.176</v>
       </c>
       <c r="E36" t="n">
-        <v>1.755</v>
+        <v>1.25</v>
       </c>
       <c r="F36" t="n">
-        <v>1.457</v>
+        <v>1.202</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>2.896</v>
+        <v>2.84</v>
       </c>
       <c r="E37" t="n">
-        <v>3.071</v>
+        <v>2.972</v>
       </c>
       <c r="F37" t="n">
-        <v>2.92</v>
+        <v>2.864</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>3.007</v>
+        <v>3.92</v>
       </c>
       <c r="E38" t="n">
-        <v>3.189</v>
+        <v>4.284</v>
       </c>
       <c r="F38" t="n">
-        <v>3.028</v>
+        <v>3.989</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>1.862</v>
+        <v>1.869</v>
       </c>
       <c r="E39" t="n">
-        <v>2.024</v>
+        <v>1.959</v>
       </c>
       <c r="F39" t="n">
-        <v>1.886</v>
+        <v>1.894</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>2.486</v>
+        <v>2.347</v>
       </c>
       <c r="E40" t="n">
-        <v>4.036</v>
+        <v>2.401</v>
       </c>
       <c r="F40" t="n">
-        <v>2.758</v>
+        <v>2.354</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>3.129</v>
+        <v>2.884</v>
       </c>
       <c r="E41" t="n">
-        <v>3.619</v>
+        <v>3.703</v>
       </c>
       <c r="F41" t="n">
-        <v>3.144</v>
+        <v>2.95</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_10000.xlsx
+++ b/exports/performance_run_10000.xlsx
@@ -485,13 +485,13 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.208</v>
+        <v>0.177</v>
       </c>
       <c r="E2" t="n">
-        <v>0.291</v>
+        <v>0.211</v>
       </c>
       <c r="F2" t="n">
-        <v>0.225</v>
+        <v>0.189</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.337</v>
+        <v>0.424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.373</v>
+        <v>0.508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.345</v>
+        <v>0.45</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>11610</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="E4" t="n">
-        <v>0.054</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,19 +575,19 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>4.463</v>
+        <v>2.392</v>
       </c>
       <c r="E5" t="n">
-        <v>4.526</v>
+        <v>2.547</v>
       </c>
       <c r="F5" t="n">
-        <v>4.458</v>
+        <v>2.424</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>54660</v>
+        <v>50280</v>
       </c>
     </row>
     <row r="6">
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.409</v>
+        <v>0.445</v>
       </c>
       <c r="E6" t="n">
-        <v>0.445</v>
+        <v>0.463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.422</v>
+        <v>0.441</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>20460</v>
+        <v>21120</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>2.001</v>
+        <v>1.189</v>
       </c>
       <c r="E7" t="n">
-        <v>2.138</v>
+        <v>1.248</v>
       </c>
       <c r="F7" t="n">
-        <v>2.032</v>
+        <v>1.198</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>27810</v>
+        <v>26220</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>6.454</v>
+        <v>6.449</v>
       </c>
       <c r="E8" t="n">
-        <v>7.728</v>
+        <v>7.964</v>
       </c>
       <c r="F8" t="n">
-        <v>6.667</v>
+        <v>6.848</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,10 +695,10 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>0.29</v>
+        <v>0.288</v>
       </c>
       <c r="E9" t="n">
-        <v>0.342</v>
+        <v>0.337</v>
       </c>
       <c r="F9" t="n">
         <v>0.302</v>
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>0.149</v>
+        <v>0.154</v>
       </c>
       <c r="E10" t="n">
-        <v>0.178</v>
+        <v>0.196</v>
       </c>
       <c r="F10" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>11640</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="11">
@@ -755,13 +755,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>3.128</v>
+        <v>3.404</v>
       </c>
       <c r="E11" t="n">
-        <v>3.333</v>
+        <v>3.527</v>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>3.656</v>
+        <v>2.891</v>
       </c>
       <c r="E12" t="n">
-        <v>3.979</v>
+        <v>3.084</v>
       </c>
       <c r="F12" t="n">
-        <v>3.517</v>
+        <v>2.919</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>3.395</v>
+        <v>3.343</v>
       </c>
       <c r="E13" t="n">
-        <v>4.237</v>
+        <v>3.521</v>
       </c>
       <c r="F13" t="n">
-        <v>3.433</v>
+        <v>3.258</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>2.573</v>
+        <v>2.285</v>
       </c>
       <c r="E14" t="n">
-        <v>2.885</v>
+        <v>2.44</v>
       </c>
       <c r="F14" t="n">
-        <v>2.514</v>
+        <v>2.304</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>7.692</v>
       </c>
       <c r="E15" t="n">
-        <v>8.667</v>
+        <v>11.336</v>
       </c>
       <c r="F15" t="n">
-        <v>7.852</v>
+        <v>8.616</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>6.256</v>
+        <v>5.843</v>
       </c>
       <c r="E16" t="n">
-        <v>7.107</v>
+        <v>6.988</v>
       </c>
       <c r="F16" t="n">
-        <v>6.15</v>
+        <v>5.725</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>4.153</v>
+        <v>3.968</v>
       </c>
       <c r="E17" t="n">
-        <v>4.741</v>
+        <v>6.774</v>
       </c>
       <c r="F17" t="n">
-        <v>4.231</v>
+        <v>4.583</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>6.307</v>
+        <v>6.166</v>
       </c>
       <c r="E18" t="n">
-        <v>8.903</v>
+        <v>6.453</v>
       </c>
       <c r="F18" t="n">
-        <v>7.134</v>
+        <v>6.179</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>2.808</v>
+        <v>2.747</v>
       </c>
       <c r="E19" t="n">
-        <v>3.16</v>
+        <v>2.956</v>
       </c>
       <c r="F19" t="n">
-        <v>2.859</v>
+        <v>2.764</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>4.582</v>
+        <v>3.062</v>
       </c>
       <c r="E20" t="n">
-        <v>6.979</v>
+        <v>3.557</v>
       </c>
       <c r="F20" t="n">
-        <v>4.834</v>
+        <v>3.183</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>6.037</v>
+        <v>5.148</v>
       </c>
       <c r="E21" t="n">
-        <v>7.621</v>
+        <v>6.969</v>
       </c>
       <c r="F21" t="n">
-        <v>6.168</v>
+        <v>5.477</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>0.155</v>
+        <v>0.151</v>
       </c>
       <c r="E22" t="n">
-        <v>0.161</v>
+        <v>0.181</v>
       </c>
       <c r="F22" t="n">
-        <v>0.159</v>
+        <v>0.162</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>11640</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>0.313</v>
+        <v>0.369</v>
       </c>
       <c r="E23" t="n">
-        <v>0.355</v>
+        <v>0.538</v>
       </c>
       <c r="F23" t="n">
-        <v>0.313</v>
+        <v>0.401</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>11580</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="24">
@@ -1148,7 +1148,7 @@
         <v>0.036</v>
       </c>
       <c r="E24" t="n">
-        <v>0.041</v>
+        <v>0.037</v>
       </c>
       <c r="F24" t="n">
         <v>0.037</v>
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>5.749</v>
+        <v>1.751</v>
       </c>
       <c r="E25" t="n">
-        <v>5.946</v>
+        <v>1.977</v>
       </c>
       <c r="F25" t="n">
-        <v>5.776</v>
+        <v>1.771</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>15480</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>0.362</v>
+        <v>0.38</v>
       </c>
       <c r="E26" t="n">
-        <v>0.409</v>
+        <v>0.422</v>
       </c>
       <c r="F26" t="n">
-        <v>0.355</v>
+        <v>0.372</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>12450</v>
+        <v>13140</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>3.21</v>
+        <v>0.905</v>
       </c>
       <c r="E27" t="n">
-        <v>3.327</v>
+        <v>1.739</v>
       </c>
       <c r="F27" t="n">
-        <v>3.229</v>
+        <v>1.096</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>15870</v>
+        <v>14220</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>4.046</v>
+        <v>3.816</v>
       </c>
       <c r="E28" t="n">
-        <v>4.416</v>
+        <v>4.057</v>
       </c>
       <c r="F28" t="n">
-        <v>3.992</v>
+        <v>3.851</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>0.254</v>
+        <v>0.261</v>
       </c>
       <c r="E29" t="n">
-        <v>0.416</v>
+        <v>0.295</v>
       </c>
       <c r="F29" t="n">
-        <v>0.285</v>
+        <v>0.268</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>11610</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>0.327</v>
+        <v>0.308</v>
       </c>
       <c r="E30" t="n">
-        <v>0.383</v>
+        <v>0.364</v>
       </c>
       <c r="F30" t="n">
-        <v>0.342</v>
+        <v>0.311</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>11580</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>2.476</v>
+        <v>2.384</v>
       </c>
       <c r="E31" t="n">
-        <v>2.797</v>
+        <v>2.789</v>
       </c>
       <c r="F31" t="n">
-        <v>2.529</v>
+        <v>2.449</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>1.062</v>
+        <v>1.009</v>
       </c>
       <c r="E32" t="n">
-        <v>1.248</v>
+        <v>1.122</v>
       </c>
       <c r="F32" t="n">
-        <v>1.101</v>
+        <v>1.025</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>2.106</v>
+        <v>2.085</v>
       </c>
       <c r="E33" t="n">
-        <v>2.283</v>
+        <v>2.162</v>
       </c>
       <c r="F33" t="n">
-        <v>2.131</v>
+        <v>2.103</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>1.042</v>
+        <v>0.993</v>
       </c>
       <c r="E34" t="n">
-        <v>1.091</v>
+        <v>1.045</v>
       </c>
       <c r="F34" t="n">
-        <v>1.05</v>
+        <v>1.001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>5.947</v>
+        <v>5.83</v>
       </c>
       <c r="E35" t="n">
-        <v>6.278</v>
+        <v>6.112</v>
       </c>
       <c r="F35" t="n">
-        <v>5.982</v>
+        <v>5.856</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>1.176</v>
+        <v>1.168</v>
       </c>
       <c r="E36" t="n">
-        <v>1.25</v>
+        <v>1.193</v>
       </c>
       <c r="F36" t="n">
-        <v>1.202</v>
+        <v>1.172</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>2.84</v>
+        <v>3.17</v>
       </c>
       <c r="E37" t="n">
-        <v>2.972</v>
+        <v>3.893</v>
       </c>
       <c r="F37" t="n">
-        <v>2.864</v>
+        <v>3.306</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>3.92</v>
+        <v>3.911</v>
       </c>
       <c r="E38" t="n">
-        <v>4.284</v>
+        <v>4.04</v>
       </c>
       <c r="F38" t="n">
-        <v>3.989</v>
+        <v>3.929</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>1.869</v>
+        <v>1.854</v>
       </c>
       <c r="E39" t="n">
-        <v>1.959</v>
+        <v>2.713</v>
       </c>
       <c r="F39" t="n">
-        <v>1.894</v>
+        <v>1.992</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>2.347</v>
+        <v>2.216</v>
       </c>
       <c r="E40" t="n">
-        <v>2.401</v>
+        <v>2.296</v>
       </c>
       <c r="F40" t="n">
-        <v>2.354</v>
+        <v>2.22</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>2.884</v>
+        <v>2.373</v>
       </c>
       <c r="E41" t="n">
-        <v>3.703</v>
+        <v>2.524</v>
       </c>
       <c r="F41" t="n">
-        <v>2.95</v>
+        <v>2.402</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_10000.xlsx
+++ b/exports/performance_run_10000.xlsx
@@ -485,13 +485,13 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.177</v>
+        <v>0.425</v>
       </c>
       <c r="E2" t="n">
-        <v>0.211</v>
+        <v>0.492</v>
       </c>
       <c r="F2" t="n">
-        <v>0.189</v>
+        <v>0.447</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.424</v>
+        <v>1.206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.508</v>
+        <v>1.49</v>
       </c>
       <c r="F3" t="n">
-        <v>0.45</v>
+        <v>1.203</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>11670</v>
+        <v>11820</v>
       </c>
     </row>
     <row r="4">
@@ -545,19 +545,19 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.052</v>
+        <v>0.117</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08</v>
+        <v>0.177</v>
       </c>
       <c r="F4" t="n">
-        <v>0.055</v>
+        <v>0.129</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>630</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5">
@@ -575,19 +575,19 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>2.392</v>
+        <v>5.918</v>
       </c>
       <c r="E5" t="n">
-        <v>2.547</v>
+        <v>6.245</v>
       </c>
       <c r="F5" t="n">
-        <v>2.424</v>
+        <v>5.948</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>50280</v>
+        <v>50670</v>
       </c>
     </row>
     <row r="6">
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.445</v>
+        <v>1.047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.463</v>
+        <v>1.088</v>
       </c>
       <c r="F6" t="n">
-        <v>0.441</v>
+        <v>1.056</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>21120</v>
+        <v>21810</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>1.189</v>
+        <v>2.805</v>
       </c>
       <c r="E7" t="n">
-        <v>1.248</v>
+        <v>3.52</v>
       </c>
       <c r="F7" t="n">
-        <v>1.198</v>
+        <v>2.934</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>26220</v>
+        <v>26370</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>6.449</v>
+        <v>14.411</v>
       </c>
       <c r="E8" t="n">
-        <v>7.964</v>
+        <v>14.94</v>
       </c>
       <c r="F8" t="n">
-        <v>6.848</v>
+        <v>14.502</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>0.288</v>
+        <v>0.829</v>
       </c>
       <c r="E9" t="n">
-        <v>0.337</v>
+        <v>0.877</v>
       </c>
       <c r="F9" t="n">
-        <v>0.302</v>
+        <v>0.826</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>11670</v>
+        <v>11820</v>
       </c>
     </row>
     <row r="10">
@@ -725,13 +725,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>0.154</v>
+        <v>0.362</v>
       </c>
       <c r="E10" t="n">
-        <v>0.196</v>
+        <v>0.444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.16</v>
+        <v>0.389</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>3.404</v>
+        <v>7.948</v>
       </c>
       <c r="E11" t="n">
-        <v>3.527</v>
+        <v>8.178000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.41</v>
+        <v>7.964</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>50640</v>
+        <v>52080</v>
       </c>
     </row>
     <row r="12">
@@ -785,19 +785,19 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>2.891</v>
+        <v>6.619</v>
       </c>
       <c r="E12" t="n">
-        <v>3.084</v>
+        <v>6.861</v>
       </c>
       <c r="F12" t="n">
-        <v>2.919</v>
+        <v>6.658</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>49920</v>
+        <v>99840</v>
       </c>
     </row>
     <row r="13">
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>3.343</v>
+        <v>6.411</v>
       </c>
       <c r="E13" t="n">
-        <v>3.521</v>
+        <v>6.709</v>
       </c>
       <c r="F13" t="n">
-        <v>3.258</v>
+        <v>6.459</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>2.285</v>
+        <v>6.27</v>
       </c>
       <c r="E14" t="n">
-        <v>2.44</v>
+        <v>7.599</v>
       </c>
       <c r="F14" t="n">
-        <v>2.304</v>
+        <v>6.152</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>7.692</v>
+        <v>17.979</v>
       </c>
       <c r="E15" t="n">
-        <v>11.336</v>
+        <v>18.963</v>
       </c>
       <c r="F15" t="n">
-        <v>8.616</v>
+        <v>18.101</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>5.843</v>
+        <v>11.254</v>
       </c>
       <c r="E16" t="n">
-        <v>6.988</v>
+        <v>11.798</v>
       </c>
       <c r="F16" t="n">
-        <v>5.725</v>
+        <v>11.263</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>3.968</v>
+        <v>10.012</v>
       </c>
       <c r="E17" t="n">
-        <v>6.774</v>
+        <v>10.901</v>
       </c>
       <c r="F17" t="n">
-        <v>4.583</v>
+        <v>9.868</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>6.166</v>
+        <v>14.125</v>
       </c>
       <c r="E18" t="n">
-        <v>6.453</v>
+        <v>14.345</v>
       </c>
       <c r="F18" t="n">
-        <v>6.179</v>
+        <v>14.124</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>2.747</v>
+        <v>6.314</v>
       </c>
       <c r="E19" t="n">
-        <v>2.956</v>
+        <v>8.932</v>
       </c>
       <c r="F19" t="n">
-        <v>2.764</v>
+        <v>6.598</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>3.062</v>
+        <v>6.608</v>
       </c>
       <c r="E20" t="n">
-        <v>3.557</v>
+        <v>6.932</v>
       </c>
       <c r="F20" t="n">
-        <v>3.183</v>
+        <v>6.67</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>5.148</v>
+        <v>11.869</v>
       </c>
       <c r="E21" t="n">
-        <v>6.969</v>
+        <v>12.27</v>
       </c>
       <c r="F21" t="n">
-        <v>5.477</v>
+        <v>11.922</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>0.151</v>
+        <v>0.154</v>
       </c>
       <c r="E22" t="n">
-        <v>0.181</v>
+        <v>0.21</v>
       </c>
       <c r="F22" t="n">
         <v>0.162</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>11670</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>0.369</v>
+        <v>0.189</v>
       </c>
       <c r="E23" t="n">
-        <v>0.538</v>
+        <v>0.246</v>
       </c>
       <c r="F23" t="n">
-        <v>0.401</v>
+        <v>0.199</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>11670</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
@@ -1145,19 +1145,19 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.036</v>
+        <v>0.065</v>
       </c>
       <c r="E24" t="n">
-        <v>0.037</v>
+        <v>0.126</v>
       </c>
       <c r="F24" t="n">
-        <v>0.037</v>
+        <v>0.073</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25">
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>1.751</v>
+        <v>13.25</v>
       </c>
       <c r="E25" t="n">
-        <v>1.977</v>
+        <v>13.435</v>
       </c>
       <c r="F25" t="n">
-        <v>1.771</v>
+        <v>13.258</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>15900</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>0.38</v>
+        <v>0.255</v>
       </c>
       <c r="E26" t="n">
-        <v>0.422</v>
+        <v>0.328</v>
       </c>
       <c r="F26" t="n">
-        <v>0.372</v>
+        <v>0.279</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>13140</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>0.905</v>
+        <v>1.442</v>
       </c>
       <c r="E27" t="n">
-        <v>1.739</v>
+        <v>1.488</v>
       </c>
       <c r="F27" t="n">
-        <v>1.096</v>
+        <v>1.445</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>14220</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>3.816</v>
+        <v>8.747</v>
       </c>
       <c r="E28" t="n">
-        <v>4.057</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>3.851</v>
+        <v>8.827999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>0.261</v>
+        <v>0.149</v>
       </c>
       <c r="E29" t="n">
-        <v>0.295</v>
+        <v>0.151</v>
       </c>
       <c r="F29" t="n">
-        <v>0.268</v>
+        <v>0.149</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>11670</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>0.308</v>
+        <v>0.157</v>
       </c>
       <c r="E30" t="n">
-        <v>0.364</v>
+        <v>0.22</v>
       </c>
       <c r="F30" t="n">
-        <v>0.311</v>
+        <v>0.167</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>11670</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>2.384</v>
+        <v>3.375</v>
       </c>
       <c r="E31" t="n">
-        <v>2.789</v>
+        <v>3.477</v>
       </c>
       <c r="F31" t="n">
-        <v>2.449</v>
+        <v>3.396</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>15510</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>1.009</v>
+        <v>2.257</v>
       </c>
       <c r="E32" t="n">
-        <v>1.122</v>
+        <v>2.333</v>
       </c>
       <c r="F32" t="n">
-        <v>1.025</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>15510</v>
+        <v>30960</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>2.085</v>
+        <v>4.686</v>
       </c>
       <c r="E33" t="n">
-        <v>2.162</v>
+        <v>4.997</v>
       </c>
       <c r="F33" t="n">
-        <v>2.103</v>
+        <v>4.756</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>0.993</v>
+        <v>2.247</v>
       </c>
       <c r="E34" t="n">
-        <v>1.045</v>
+        <v>3.051</v>
       </c>
       <c r="F34" t="n">
-        <v>1.001</v>
+        <v>2.367</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>5.83</v>
+        <v>13.682</v>
       </c>
       <c r="E35" t="n">
-        <v>6.112</v>
+        <v>14.142</v>
       </c>
       <c r="F35" t="n">
-        <v>5.856</v>
+        <v>13.681</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>1.168</v>
+        <v>2.715</v>
       </c>
       <c r="E36" t="n">
-        <v>1.193</v>
+        <v>3.16</v>
       </c>
       <c r="F36" t="n">
-        <v>1.172</v>
+        <v>2.831</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>3.17</v>
+        <v>6.423</v>
       </c>
       <c r="E37" t="n">
-        <v>3.893</v>
+        <v>6.537</v>
       </c>
       <c r="F37" t="n">
-        <v>3.306</v>
+        <v>6.433</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>3.911</v>
+        <v>8.993</v>
       </c>
       <c r="E38" t="n">
-        <v>4.04</v>
+        <v>9.32</v>
       </c>
       <c r="F38" t="n">
-        <v>3.929</v>
+        <v>9.058</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>1.854</v>
+        <v>4.197</v>
       </c>
       <c r="E39" t="n">
-        <v>2.713</v>
+        <v>4.418</v>
       </c>
       <c r="F39" t="n">
-        <v>1.992</v>
+        <v>4.215</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>2.216</v>
+        <v>4.978</v>
       </c>
       <c r="E40" t="n">
-        <v>2.296</v>
+        <v>5.062</v>
       </c>
       <c r="F40" t="n">
-        <v>2.22</v>
+        <v>4.991</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>2.373</v>
+        <v>5.395</v>
       </c>
       <c r="E41" t="n">
-        <v>2.524</v>
+        <v>5.457</v>
       </c>
       <c r="F41" t="n">
-        <v>2.402</v>
+        <v>5.39</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_10000.xlsx
+++ b/exports/performance_run_10000.xlsx
@@ -485,13 +485,13 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.425</v>
+        <v>0.234</v>
       </c>
       <c r="E2" t="n">
-        <v>0.492</v>
+        <v>0.328</v>
       </c>
       <c r="F2" t="n">
-        <v>0.447</v>
+        <v>0.251</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -515,13 +515,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>1.206</v>
+        <v>0.673</v>
       </c>
       <c r="E3" t="n">
-        <v>1.49</v>
+        <v>0.864</v>
       </c>
       <c r="F3" t="n">
-        <v>1.203</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.117</v>
+        <v>0.052</v>
       </c>
       <c r="E4" t="n">
-        <v>0.177</v>
+        <v>0.082</v>
       </c>
       <c r="F4" t="n">
-        <v>0.129</v>
+        <v>0.056</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>5.918</v>
+        <v>2.592</v>
       </c>
       <c r="E5" t="n">
-        <v>6.245</v>
+        <v>4.207</v>
       </c>
       <c r="F5" t="n">
-        <v>5.948</v>
+        <v>2.899</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>1.047</v>
+        <v>0.473</v>
       </c>
       <c r="E6" t="n">
-        <v>1.088</v>
+        <v>0.535</v>
       </c>
       <c r="F6" t="n">
-        <v>1.056</v>
+        <v>0.477</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>21810</v>
+        <v>21870</v>
       </c>
     </row>
     <row r="7">
@@ -635,13 +635,13 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>2.805</v>
+        <v>1.231</v>
       </c>
       <c r="E7" t="n">
-        <v>3.52</v>
+        <v>1.305</v>
       </c>
       <c r="F7" t="n">
-        <v>2.934</v>
+        <v>1.251</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>14.411</v>
+        <v>8.52</v>
       </c>
       <c r="E8" t="n">
-        <v>14.94</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>14.502</v>
+        <v>8.416</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,13 +695,13 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>0.829</v>
+        <v>0.307</v>
       </c>
       <c r="E9" t="n">
-        <v>0.877</v>
+        <v>0.384</v>
       </c>
       <c r="F9" t="n">
-        <v>0.826</v>
+        <v>0.33</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>0.362</v>
+        <v>0.191</v>
       </c>
       <c r="E10" t="n">
-        <v>0.444</v>
+        <v>0.229</v>
       </c>
       <c r="F10" t="n">
-        <v>0.389</v>
+        <v>0.202</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -755,13 +755,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>7.948</v>
+        <v>5.014</v>
       </c>
       <c r="E11" t="n">
-        <v>8.178000000000001</v>
+        <v>5.278</v>
       </c>
       <c r="F11" t="n">
-        <v>7.964</v>
+        <v>5.017</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>6.619</v>
+        <v>4.367</v>
       </c>
       <c r="E12" t="n">
-        <v>6.861</v>
+        <v>5.218</v>
       </c>
       <c r="F12" t="n">
-        <v>6.658</v>
+        <v>4.488</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>6.411</v>
+        <v>3.811</v>
       </c>
       <c r="E13" t="n">
-        <v>6.709</v>
+        <v>4.946</v>
       </c>
       <c r="F13" t="n">
-        <v>6.459</v>
+        <v>4.061</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>6.27</v>
+        <v>3.1</v>
       </c>
       <c r="E14" t="n">
-        <v>7.599</v>
+        <v>3.611</v>
       </c>
       <c r="F14" t="n">
-        <v>6.152</v>
+        <v>3.165</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>17.979</v>
+        <v>11.831</v>
       </c>
       <c r="E15" t="n">
-        <v>18.963</v>
+        <v>12.424</v>
       </c>
       <c r="F15" t="n">
-        <v>18.101</v>
+        <v>11.838</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>11.254</v>
+        <v>6.826</v>
       </c>
       <c r="E16" t="n">
-        <v>11.798</v>
+        <v>7.314</v>
       </c>
       <c r="F16" t="n">
-        <v>11.263</v>
+        <v>6.802</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>10.012</v>
+        <v>4.904</v>
       </c>
       <c r="E17" t="n">
-        <v>10.901</v>
+        <v>5.05</v>
       </c>
       <c r="F17" t="n">
-        <v>9.868</v>
+        <v>4.911</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>14.125</v>
+        <v>8.554</v>
       </c>
       <c r="E18" t="n">
-        <v>14.345</v>
+        <v>9.635</v>
       </c>
       <c r="F18" t="n">
-        <v>14.124</v>
+        <v>8.68</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>6.314</v>
+        <v>3.66</v>
       </c>
       <c r="E19" t="n">
-        <v>8.932</v>
+        <v>4.692</v>
       </c>
       <c r="F19" t="n">
-        <v>6.598</v>
+        <v>3.931</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>6.608</v>
+        <v>4.5</v>
       </c>
       <c r="E20" t="n">
-        <v>6.932</v>
+        <v>4.945</v>
       </c>
       <c r="F20" t="n">
-        <v>6.67</v>
+        <v>4.452</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>11.869</v>
+        <v>7.147</v>
       </c>
       <c r="E21" t="n">
-        <v>12.27</v>
+        <v>7.905</v>
       </c>
       <c r="F21" t="n">
-        <v>11.922</v>
+        <v>7.212</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,13 +1085,13 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>0.154</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.21</v>
+        <v>0.115</v>
       </c>
       <c r="F22" t="n">
-        <v>0.162</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1115,13 +1115,13 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>0.189</v>
+        <v>0.105</v>
       </c>
       <c r="E23" t="n">
-        <v>0.246</v>
+        <v>0.138</v>
       </c>
       <c r="F23" t="n">
-        <v>0.199</v>
+        <v>0.11</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.065</v>
+        <v>0.037</v>
       </c>
       <c r="E24" t="n">
-        <v>0.126</v>
+        <v>0.038</v>
       </c>
       <c r="F24" t="n">
-        <v>0.073</v>
+        <v>0.037</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>13.25</v>
+        <v>6.956</v>
       </c>
       <c r="E25" t="n">
-        <v>13.435</v>
+        <v>8.416</v>
       </c>
       <c r="F25" t="n">
-        <v>13.258</v>
+        <v>6.993</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>0.255</v>
+        <v>0.144</v>
       </c>
       <c r="E26" t="n">
-        <v>0.328</v>
+        <v>0.173</v>
       </c>
       <c r="F26" t="n">
-        <v>0.279</v>
+        <v>0.147</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>1.442</v>
+        <v>0.719</v>
       </c>
       <c r="E27" t="n">
-        <v>1.488</v>
+        <v>0.897</v>
       </c>
       <c r="F27" t="n">
-        <v>1.445</v>
+        <v>0.721</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>14310</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>8.747</v>
+        <v>5.394</v>
       </c>
       <c r="E28" t="n">
-        <v>9.148999999999999</v>
+        <v>6.339</v>
       </c>
       <c r="F28" t="n">
-        <v>8.827999999999999</v>
+        <v>5.448</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="29">
@@ -1295,13 +1295,13 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>0.149</v>
+        <v>0.089</v>
       </c>
       <c r="E29" t="n">
-        <v>0.151</v>
+        <v>0.118</v>
       </c>
       <c r="F29" t="n">
-        <v>0.149</v>
+        <v>0.093</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1325,13 +1325,13 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.157</v>
       </c>
-      <c r="E30" t="n">
-        <v>0.22</v>
-      </c>
       <c r="F30" t="n">
-        <v>0.167</v>
+        <v>0.101</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>3.375</v>
+        <v>1.928</v>
       </c>
       <c r="E31" t="n">
-        <v>3.477</v>
+        <v>2.241</v>
       </c>
       <c r="F31" t="n">
-        <v>3.396</v>
+        <v>1.966</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2190</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>2.257</v>
+        <v>1.35</v>
       </c>
       <c r="E32" t="n">
-        <v>2.333</v>
+        <v>1.46</v>
       </c>
       <c r="F32" t="n">
-        <v>2.26</v>
+        <v>1.335</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>30960</v>
+        <v>31020</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>4.686</v>
+        <v>2.069</v>
       </c>
       <c r="E33" t="n">
-        <v>4.997</v>
+        <v>2.215</v>
       </c>
       <c r="F33" t="n">
-        <v>4.756</v>
+        <v>2.099</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>2.247</v>
+        <v>1.013</v>
       </c>
       <c r="E34" t="n">
-        <v>3.051</v>
+        <v>1.203</v>
       </c>
       <c r="F34" t="n">
-        <v>2.367</v>
+        <v>1.063</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>13.682</v>
+        <v>8.042</v>
       </c>
       <c r="E35" t="n">
-        <v>14.142</v>
+        <v>9.893000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>13.681</v>
+        <v>7.933</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>2.715</v>
+        <v>1.205</v>
       </c>
       <c r="E36" t="n">
-        <v>3.16</v>
+        <v>1.444</v>
       </c>
       <c r="F36" t="n">
-        <v>2.831</v>
+        <v>1.254</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>6.423</v>
+        <v>2.905</v>
       </c>
       <c r="E37" t="n">
-        <v>6.537</v>
+        <v>3.32</v>
       </c>
       <c r="F37" t="n">
-        <v>6.433</v>
+        <v>2.963</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>8.993</v>
+        <v>4.261</v>
       </c>
       <c r="E38" t="n">
-        <v>9.32</v>
+        <v>4.623</v>
       </c>
       <c r="F38" t="n">
-        <v>9.058</v>
+        <v>4.299</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>4.197</v>
+        <v>2.545</v>
       </c>
       <c r="E39" t="n">
-        <v>4.418</v>
+        <v>2.882</v>
       </c>
       <c r="F39" t="n">
-        <v>4.215</v>
+        <v>2.577</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>4.978</v>
+        <v>2.383</v>
       </c>
       <c r="E40" t="n">
-        <v>5.062</v>
+        <v>2.829</v>
       </c>
       <c r="F40" t="n">
-        <v>4.991</v>
+        <v>2.467</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>5.395</v>
+        <v>3.684</v>
       </c>
       <c r="E41" t="n">
-        <v>5.457</v>
+        <v>4.056</v>
       </c>
       <c r="F41" t="n">
-        <v>5.39</v>
+        <v>3.698</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_10000.xlsx
+++ b/exports/performance_run_10000.xlsx
@@ -485,13 +485,13 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.234</v>
+        <v>0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>0.328</v>
+        <v>0.391</v>
       </c>
       <c r="F2" t="n">
-        <v>0.251</v>
+        <v>0.252</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -515,13 +515,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.673</v>
+        <v>0.644</v>
       </c>
       <c r="E3" t="n">
-        <v>0.864</v>
+        <v>1.043</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.713</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
       <c r="E4" t="n">
-        <v>0.082</v>
+        <v>0.098</v>
       </c>
       <c r="F4" t="n">
-        <v>0.056</v>
+        <v>0.065</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>2.592</v>
+        <v>3.247</v>
       </c>
       <c r="E5" t="n">
-        <v>4.207</v>
+        <v>4.056</v>
       </c>
       <c r="F5" t="n">
-        <v>2.899</v>
+        <v>3.352</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.473</v>
+        <v>0.451</v>
       </c>
       <c r="E6" t="n">
-        <v>0.535</v>
+        <v>0.469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.477</v>
+        <v>0.447</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>21870</v>
+        <v>21300</v>
       </c>
     </row>
     <row r="7">
@@ -635,13 +635,13 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>1.231</v>
+        <v>1.173</v>
       </c>
       <c r="E7" t="n">
-        <v>1.305</v>
+        <v>1.601</v>
       </c>
       <c r="F7" t="n">
-        <v>1.251</v>
+        <v>1.257</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>8.52</v>
+        <v>7.016</v>
       </c>
       <c r="E8" t="n">
-        <v>8.736000000000001</v>
+        <v>9.791</v>
       </c>
       <c r="F8" t="n">
-        <v>8.416</v>
+        <v>7.578</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,13 +695,13 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>0.307</v>
+        <v>0.376</v>
       </c>
       <c r="E9" t="n">
-        <v>0.384</v>
+        <v>0.619</v>
       </c>
       <c r="F9" t="n">
-        <v>0.33</v>
+        <v>0.438</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="E10" t="n">
-        <v>0.229</v>
+        <v>0.476</v>
       </c>
       <c r="F10" t="n">
-        <v>0.202</v>
+        <v>0.247</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -755,13 +755,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>5.014</v>
+        <v>5.593</v>
       </c>
       <c r="E11" t="n">
-        <v>5.278</v>
+        <v>6.1</v>
       </c>
       <c r="F11" t="n">
-        <v>5.017</v>
+        <v>5.604</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>4.367</v>
+        <v>5.022</v>
       </c>
       <c r="E12" t="n">
-        <v>5.218</v>
+        <v>5.453</v>
       </c>
       <c r="F12" t="n">
-        <v>4.488</v>
+        <v>5.105</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>3.811</v>
+        <v>5.054</v>
       </c>
       <c r="E13" t="n">
-        <v>4.946</v>
+        <v>10.548</v>
       </c>
       <c r="F13" t="n">
-        <v>4.061</v>
+        <v>5.908</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1</v>
+        <v>4.031</v>
       </c>
       <c r="E14" t="n">
-        <v>3.611</v>
+        <v>4.455</v>
       </c>
       <c r="F14" t="n">
-        <v>3.165</v>
+        <v>4.042</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>11.831</v>
+        <v>8.156000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>12.424</v>
+        <v>11.276</v>
       </c>
       <c r="F15" t="n">
-        <v>11.838</v>
+        <v>8.922000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>6.826</v>
+        <v>5.011</v>
       </c>
       <c r="E16" t="n">
-        <v>7.314</v>
+        <v>6.037</v>
       </c>
       <c r="F16" t="n">
-        <v>6.802</v>
+        <v>5.19</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>4.904</v>
+        <v>4.186</v>
       </c>
       <c r="E17" t="n">
-        <v>5.05</v>
+        <v>5.244</v>
       </c>
       <c r="F17" t="n">
-        <v>4.911</v>
+        <v>4.348</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>8.554</v>
+        <v>8.388999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>9.635</v>
+        <v>8.881</v>
       </c>
       <c r="F18" t="n">
-        <v>8.68</v>
+        <v>7.93</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>3.66</v>
+        <v>5.1</v>
       </c>
       <c r="E19" t="n">
-        <v>4.692</v>
+        <v>5.529</v>
       </c>
       <c r="F19" t="n">
-        <v>3.931</v>
+        <v>5.117</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>4.5</v>
+        <v>5.256</v>
       </c>
       <c r="E20" t="n">
-        <v>4.945</v>
+        <v>6.319</v>
       </c>
       <c r="F20" t="n">
-        <v>4.452</v>
+        <v>5.437</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>7.147</v>
+        <v>8.522</v>
       </c>
       <c r="E21" t="n">
-        <v>7.905</v>
+        <v>10.482</v>
       </c>
       <c r="F21" t="n">
-        <v>7.212</v>
+        <v>8.831</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.123</v>
       </c>
       <c r="E22" t="n">
-        <v>0.115</v>
+        <v>0.177</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
@@ -1115,13 +1115,13 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="E23" t="n">
-        <v>0.138</v>
+        <v>0.157</v>
       </c>
       <c r="F23" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.037</v>
+        <v>0.041</v>
       </c>
       <c r="E24" t="n">
-        <v>0.038</v>
+        <v>0.076</v>
       </c>
       <c r="F24" t="n">
-        <v>0.037</v>
+        <v>0.045</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>6.956</v>
+        <v>5.719</v>
       </c>
       <c r="E25" t="n">
-        <v>8.416</v>
+        <v>5.984</v>
       </c>
       <c r="F25" t="n">
-        <v>6.993</v>
+        <v>5.743</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>0.144</v>
+        <v>0.112</v>
       </c>
       <c r="E26" t="n">
-        <v>0.173</v>
+        <v>0.141</v>
       </c>
       <c r="F26" t="n">
-        <v>0.147</v>
+        <v>0.117</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>0.719</v>
+        <v>0.639</v>
       </c>
       <c r="E27" t="n">
-        <v>0.897</v>
+        <v>0.773</v>
       </c>
       <c r="F27" t="n">
-        <v>0.721</v>
+        <v>0.67</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>14400</v>
+        <v>14280</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>5.394</v>
+        <v>3.765</v>
       </c>
       <c r="E28" t="n">
-        <v>6.339</v>
+        <v>4.311</v>
       </c>
       <c r="F28" t="n">
-        <v>5.448</v>
+        <v>3.857</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="29">
@@ -1295,13 +1295,13 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>0.089</v>
+        <v>0.095</v>
       </c>
       <c r="E29" t="n">
-        <v>0.118</v>
+        <v>0.153</v>
       </c>
       <c r="F29" t="n">
-        <v>0.093</v>
+        <v>0.104</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1325,13 +1325,13 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>0.089</v>
+        <v>0.1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.157</v>
+        <v>0.163</v>
       </c>
       <c r="F30" t="n">
-        <v>0.101</v>
+        <v>0.11</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>1.928</v>
+        <v>1.954</v>
       </c>
       <c r="E31" t="n">
-        <v>2.241</v>
+        <v>2.1</v>
       </c>
       <c r="F31" t="n">
-        <v>1.966</v>
+        <v>1.953</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2220</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>1.35</v>
+        <v>2.017</v>
       </c>
       <c r="E32" t="n">
-        <v>1.46</v>
+        <v>3.098</v>
       </c>
       <c r="F32" t="n">
-        <v>1.335</v>
+        <v>2.006</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>31020</v>
+        <v>30960</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>2.069</v>
+        <v>2.665</v>
       </c>
       <c r="E33" t="n">
-        <v>2.215</v>
+        <v>2.869</v>
       </c>
       <c r="F33" t="n">
-        <v>2.099</v>
+        <v>2.672</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>1.013</v>
+        <v>1.257</v>
       </c>
       <c r="E34" t="n">
-        <v>1.203</v>
+        <v>1.861</v>
       </c>
       <c r="F34" t="n">
-        <v>1.063</v>
+        <v>1.363</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>8.042</v>
+        <v>6.101</v>
       </c>
       <c r="E35" t="n">
-        <v>9.893000000000001</v>
+        <v>8.115</v>
       </c>
       <c r="F35" t="n">
-        <v>7.933</v>
+        <v>6.585</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>1.205</v>
+        <v>1.103</v>
       </c>
       <c r="E36" t="n">
-        <v>1.444</v>
+        <v>1.164</v>
       </c>
       <c r="F36" t="n">
-        <v>1.254</v>
+        <v>1.109</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>2.905</v>
+        <v>2.776</v>
       </c>
       <c r="E37" t="n">
-        <v>3.32</v>
+        <v>2.846</v>
       </c>
       <c r="F37" t="n">
-        <v>2.963</v>
+        <v>2.776</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>4.261</v>
+        <v>5.306</v>
       </c>
       <c r="E38" t="n">
-        <v>4.623</v>
+        <v>5.883</v>
       </c>
       <c r="F38" t="n">
-        <v>4.299</v>
+        <v>5.135</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>2.545</v>
+        <v>2.903</v>
       </c>
       <c r="E39" t="n">
-        <v>2.882</v>
+        <v>3.236</v>
       </c>
       <c r="F39" t="n">
-        <v>2.577</v>
+        <v>2.914</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>2.383</v>
+        <v>3.076</v>
       </c>
       <c r="E40" t="n">
-        <v>2.829</v>
+        <v>4.434</v>
       </c>
       <c r="F40" t="n">
-        <v>2.467</v>
+        <v>3.256</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>3.684</v>
+        <v>3.283</v>
       </c>
       <c r="E41" t="n">
-        <v>4.056</v>
+        <v>3.569</v>
       </c>
       <c r="F41" t="n">
-        <v>3.698</v>
+        <v>3.254</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
     </row>
   </sheetData>
